--- a/ModExcel/D道具表.xlsx
+++ b/ModExcel/D道具表.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\survivors\data\Mod表格数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5EA248-32AF-4DBE-810E-F3ED922ECC47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3356573-2B94-40E3-999D-790ECC7843F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="道具表" sheetId="25" r:id="rId1"/>
+    <sheet name="杂物表" sheetId="25" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
@@ -2695,7 +2695,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2794,6 +2794,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2823,7 +2835,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2951,6 +2963,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2963,7 +2988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3148,6 +3173,9 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3168,14 +3196,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3184,6 +3204,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3193,10 +3221,10 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3320,76 +3348,6 @@
     <cellStyle name="常规 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
   <dxfs count="41">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3834,6 +3792,76 @@
       </font>
       <alignment horizontal="left"/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3915,106 +3943,106 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="D4:AK205" tableType="xml" totalsRowShown="0" connectionId="112">
   <autoFilter ref="D4:AK205" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="33">
       <xmlColumnPr mapId="1085" xpath="/root/data/id_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="name_i" name="name_i" dataDxfId="39">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="name_i" name="name_i" dataDxfId="32">
       <xmlColumnPr mapId="1085" xpath="/root/data/name_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" uniqueName="dis_i" name="dis_i" dataDxfId="38">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" uniqueName="dis_i" name="dis_i" dataDxfId="31">
       <xmlColumnPr mapId="1085" xpath="/root/data/dis_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="dis2_i" name="dis2_i" dataDxfId="37">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="dis2_i" name="dis2_i" dataDxfId="30">
       <xmlColumnPr mapId="1085" xpath="/root/data/dis2_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="book_descri_m" name="book_descri_m" dataDxfId="36">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="book_descri_m" name="book_descri_m" dataDxfId="29">
       <xmlColumnPr mapId="1085" xpath="/root/data/book_descri_m" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="book_icon_i" name="book_icon_i" dataDxfId="35">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="book_icon_i" name="book_icon_i" dataDxfId="28">
       <xmlColumnPr mapId="1085" xpath="/root/data/book_icon_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" uniqueName="quality_i" name="quality_i" dataDxfId="34">
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" uniqueName="quality_i" name="quality_i" dataDxfId="27">
       <xmlColumnPr mapId="1085" xpath="/root/data/quality_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="icon_i" name="icon_i" dataDxfId="33">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="icon_i" name="icon_i" dataDxfId="26">
       <xmlColumnPr mapId="1085" xpath="/root/data/icon_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" uniqueName="invwidth_i" name="invwidth_i" dataDxfId="32">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" uniqueName="invwidth_i" name="invwidth_i" dataDxfId="25">
       <xmlColumnPr mapId="1085" xpath="/root/data/invwidth_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" uniqueName="invheight_i" name="invheight_i" dataDxfId="31">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" uniqueName="invheight_i" name="invheight_i" dataDxfId="24">
       <xmlColumnPr mapId="1085" xpath="/root/data/invheight_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" uniqueName="type_s" name="type_s" dataDxfId="30">
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" uniqueName="type_s" name="type_s" dataDxfId="23">
       <xmlColumnPr mapId="1085" xpath="/root/data/type_s" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" uniqueName="type2_s" name="type2_s" dataDxfId="29">
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" uniqueName="type2_s" name="type2_s" dataDxfId="22">
       <xmlColumnPr mapId="1085" xpath="/root/data/type2_s" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" uniqueName="type_name_i" name="type_name_i" dataDxfId="28">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" uniqueName="type_name_i" name="type_name_i" dataDxfId="21">
       <xmlColumnPr mapId="1085" xpath="/root/data/type_name_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" uniqueName="stackable_i" name="stackable_i" dataDxfId="27">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" uniqueName="stackable_i" name="stackable_i" dataDxfId="20">
       <xmlColumnPr mapId="1085" xpath="/root/data/stackable_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" uniqueName="minstack_i" name="minstack_i" dataDxfId="26">
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" uniqueName="minstack_i" name="minstack_i" dataDxfId="19">
       <xmlColumnPr mapId="1085" xpath="/root/data/minstack_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" uniqueName="maxstack_i" name="maxstack_i" dataDxfId="25">
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" uniqueName="maxstack_i" name="maxstack_i" dataDxfId="18">
       <xmlColumnPr mapId="1085" xpath="/root/data/maxstack_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="sale_i" name="sale_i" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="sale_i" name="sale_i" dataDxfId="17">
       <xmlColumnPr mapId="1085" xpath="/root/data/sale_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" uniqueName="cost_i" name="cost_i" dataDxfId="23">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" uniqueName="cost_i" name="cost_i" dataDxfId="16">
       <xmlColumnPr mapId="1085" xpath="/root/data/cost_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" uniqueName="discard_i" name="discard_i" dataDxfId="22">
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" uniqueName="discard_i" name="discard_i" dataDxfId="15">
       <xmlColumnPr mapId="1085" xpath="/root/data/discard_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" uniqueName="flippyfile_i" name="flippyfile_i" dataDxfId="21">
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" uniqueName="flippyfile_i" name="flippyfile_i" dataDxfId="14">
       <xmlColumnPr mapId="1085" xpath="/root/data/flippyfile_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{534CD282-FC30-4AEA-9CB1-A50ABAEB0290}" uniqueName="map_show_i" name="map_show_i" dataDxfId="20">
+    <tableColumn id="14" xr3:uid="{534CD282-FC30-4AEA-9CB1-A50ABAEB0290}" uniqueName="map_show_i" name="map_show_i" dataDxfId="13">
       <xmlColumnPr mapId="1085" xpath="/root/data/map_show_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" uniqueName="dropsound_i" name="dropsound_i" dataDxfId="19">
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" uniqueName="dropsound_i" name="dropsound_i" dataDxfId="12">
       <xmlColumnPr mapId="1085" xpath="/root/data/dropsound_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" uniqueName="pickupsound_i" name="pickupsound_i" dataDxfId="18">
+    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" uniqueName="pickupsound_i" name="pickupsound_i" dataDxfId="11">
       <xmlColumnPr mapId="1085" xpath="/root/data/pickupsound_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" uniqueName="dropsfxframe_i" name="dropsfxframe_i" dataDxfId="17">
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" uniqueName="dropsfxframe_i" name="dropsfxframe_i" dataDxfId="10">
       <xmlColumnPr mapId="1085" xpath="/root/data/dropsfxframe_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" uniqueName="usesound_i" name="usesound_i" dataDxfId="16">
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" uniqueName="usesound_i" name="usesound_i" dataDxfId="9">
       <xmlColumnPr mapId="1085" xpath="/root/data/usesound_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" uniqueName="pSpell_i" name="pSpell_i" dataDxfId="15">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" uniqueName="pSpell_i" name="pSpell_i" dataDxfId="8">
       <xmlColumnPr mapId="1085" xpath="/root/data/pSpell_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" uniqueName="item_effect_n" name="item_effect_n" dataDxfId="14">
+    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" uniqueName="item_effect_n" name="item_effect_n" dataDxfId="7">
       <xmlColumnPr mapId="1085" xpath="/root/data/item_effect_n" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" uniqueName="state_l" name="state_l" dataDxfId="13">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" uniqueName="state_l" name="state_l" dataDxfId="6">
       <xmlColumnPr mapId="1085" xpath="/root/data/state_l" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3E8B4997-960F-4C1A-B055-286195EB7D8D}" uniqueName="auto_pickup_i" name="auto_pickup_i" dataDxfId="12">
+    <tableColumn id="8" xr3:uid="{3E8B4997-960F-4C1A-B055-286195EB7D8D}" uniqueName="auto_pickup_i" name="auto_pickup_i" dataDxfId="5">
       <xmlColumnPr mapId="1085" xpath="/root/data/auto_pickup_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E62A0014-7EC8-4A74-9BA8-45A7607CC164}" uniqueName="pickup_buff_i" name="pickup_buff_i" dataDxfId="11">
+    <tableColumn id="9" xr3:uid="{E62A0014-7EC8-4A74-9BA8-45A7607CC164}" uniqueName="pickup_buff_i" name="pickup_buff_i" dataDxfId="4">
       <xmlColumnPr mapId="1085" xpath="/root/data/pickup_buff_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6F9DC695-3D3F-43F0-BB39-B43E92591111}" uniqueName="task_item_i" name="task_item_i" dataDxfId="10">
+    <tableColumn id="11" xr3:uid="{6F9DC695-3D3F-43F0-BB39-B43E92591111}" uniqueName="task_item_i" name="task_item_i" dataDxfId="3">
       <xmlColumnPr mapId="1085" xpath="/root/data/task_item_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{03B0C5E2-068D-498B-BC7B-FB44BA8BCDD6}" uniqueName="task_complete_i" name="task_complete_i" dataDxfId="9">
+    <tableColumn id="12" xr3:uid="{03B0C5E2-068D-498B-BC7B-FB44BA8BCDD6}" uniqueName="task_complete_i" name="task_complete_i" dataDxfId="2">
       <xmlColumnPr mapId="1085" xpath="/root/data/task_complete_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0BCE783B-69A8-402E-AF57-5A57901AC117}" uniqueName="task_id_i" name="task_id_i" dataDxfId="8">
+    <tableColumn id="10" xr3:uid="{0BCE783B-69A8-402E-AF57-5A57901AC117}" uniqueName="task_id_i" name="task_id_i" dataDxfId="1">
       <xmlColumnPr mapId="1085" xpath="/root/data/task_id_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BD25696F-2F12-4734-B834-508CE700C525}" uniqueName="discard_task_i" name="discard_task_i" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{BD25696F-2F12-4734-B834-508CE700C525}" uniqueName="discard_task_i" name="discard_task_i" dataDxfId="0">
       <xmlColumnPr mapId="1085" xpath="/root/data/discard_task_i" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -4310,7 +4338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AO205"/>
+  <dimension ref="A1:AQ205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" style="1" customWidth="1"/>
@@ -4335,15 +4363,17 @@
     <col min="34" max="34" width="25.375" style="2" customWidth="1"/>
     <col min="35" max="35" width="24.5" style="2" customWidth="1"/>
     <col min="36" max="37" width="27.125" style="2" customWidth="1"/>
-    <col min="39" max="39" width="30.375" style="2" customWidth="1"/>
-    <col min="40" max="40" width="25.25" style="2" customWidth="1"/>
-    <col min="41" max="41" width="19" style="3" customWidth="1"/>
-    <col min="42" max="42" width="27.375" style="2" customWidth="1"/>
-    <col min="43" max="43" width="22" style="2" customWidth="1"/>
-    <col min="44" max="16384" width="9" style="2"/>
+    <col min="39" max="39" width="21.25" style="2" customWidth="1"/>
+    <col min="40" max="40" width="26.125" style="2" customWidth="1"/>
+    <col min="41" max="41" width="30.375" style="2" customWidth="1"/>
+    <col min="42" max="42" width="25.25" style="2" customWidth="1"/>
+    <col min="43" max="43" width="19" style="3" customWidth="1"/>
+    <col min="44" max="44" width="27.375" style="2" customWidth="1"/>
+    <col min="45" max="45" width="22" style="2" customWidth="1"/>
+    <col min="46" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -4360,59 +4390,59 @@
       <c r="AD1" s="2"/>
       <c r="AE1" s="3"/>
       <c r="AL1" s="2"/>
-      <c r="AO1" s="2"/>
+      <c r="AQ1" s="2"/>
     </row>
-    <row r="2" spans="1:41" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="122" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="127" t="s">
+    <row r="2" spans="1:43" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="128" t="s">
+      <c r="R2" s="130"/>
+      <c r="S2" s="130"/>
+      <c r="T2" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="129"/>
-      <c r="V2" s="129"/>
-      <c r="W2" s="130"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="131" t="s">
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="133"/>
+      <c r="X2" s="103"/>
+      <c r="Y2" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="132"/>
-      <c r="AA2" s="132"/>
-      <c r="AB2" s="133"/>
-      <c r="AC2" s="121" t="s">
+      <c r="Z2" s="135"/>
+      <c r="AA2" s="135"/>
+      <c r="AB2" s="136"/>
+      <c r="AC2" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="121"/>
-      <c r="AE2" s="121"/>
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="124"/>
       <c r="AF2" s="31"/>
       <c r="AG2" s="31"/>
-      <c r="AH2" s="102"/>
-      <c r="AI2" s="103"/>
-      <c r="AJ2" s="104"/>
-      <c r="AK2" s="96"/>
+      <c r="AH2" s="105"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="107"/>
+      <c r="AK2" s="99"/>
       <c r="AL2" s="2"/>
-      <c r="AO2" s="2"/>
+      <c r="AQ2" s="2"/>
     </row>
-    <row r="3" spans="1:41" ht="150.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" ht="150.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4514,9 +4544,9 @@
         <v>332</v>
       </c>
       <c r="AL3" s="2"/>
-      <c r="AO3" s="2"/>
+      <c r="AQ3" s="2"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="36"/>
       <c r="B4" s="37"/>
       <c r="C4" s="36"/>
@@ -4623,9 +4653,9 @@
         <v>333</v>
       </c>
       <c r="AL4" s="2"/>
-      <c r="AO4" s="2"/>
+      <c r="AQ4" s="2"/>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="35"/>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
@@ -4732,9 +4762,9 @@
         <v>0</v>
       </c>
       <c r="AL5" s="2"/>
-      <c r="AO5" s="2"/>
+      <c r="AQ5" s="2"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="40"/>
       <c r="B6" s="40" t="s">
         <v>50</v>
@@ -4809,9 +4839,9 @@
       <c r="AD6" s="29"/>
       <c r="AE6" s="9"/>
       <c r="AL6" s="2"/>
-      <c r="AO6" s="2"/>
+      <c r="AQ6" s="2"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="40"/>
       <c r="B7" s="40" t="s">
         <v>53</v>
@@ -4888,9 +4918,9 @@
       <c r="AD7" s="29"/>
       <c r="AE7" s="9"/>
       <c r="AL7" s="2"/>
-      <c r="AO7" s="2"/>
+      <c r="AQ7" s="2"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
       <c r="B8" s="40" t="s">
         <v>55</v>
@@ -4967,9 +4997,9 @@
       <c r="AD8" s="29"/>
       <c r="AE8" s="9"/>
       <c r="AL8" s="2"/>
-      <c r="AO8" s="2"/>
+      <c r="AQ8" s="2"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="42" t="s">
         <v>58</v>
@@ -5047,7 +5077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="41"/>
       <c r="B10" s="42" t="s">
         <v>75</v>
@@ -5125,7 +5155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="42" t="s">
         <v>83</v>
@@ -5208,7 +5238,7 @@
         <v>5011</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="41"/>
       <c r="B12" s="42" t="s">
         <v>176</v>
@@ -5289,7 +5319,7 @@
         <v>5012</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="42" t="s">
         <v>222</v>
@@ -5367,7 +5397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="41"/>
       <c r="B14" s="42" t="s">
         <v>309</v>
@@ -5443,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>66</v>
       </c>
@@ -5517,7 +5547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
         <v>66</v>
       </c>
@@ -5594,7 +5624,7 @@
         <v>5001</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
         <v>66</v>
       </c>
@@ -5671,7 +5701,7 @@
         <v>5002</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="41"/>
       <c r="B18" s="42"/>
       <c r="C18" s="41" t="s">
@@ -5747,7 +5777,7 @@
       <c r="AE18" s="30"/>
       <c r="AF18" s="14"/>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" s="40"/>
       <c r="B19" s="40" t="s">
         <v>352</v>
@@ -5824,9 +5854,9 @@
       <c r="AD19" s="29"/>
       <c r="AE19" s="9"/>
       <c r="AL19" s="2"/>
-      <c r="AO19" s="2"/>
+      <c r="AQ19" s="2"/>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="72"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74" t="s">
@@ -5901,8 +5931,8 @@
       <c r="AD20" s="29"/>
       <c r="AE20" s="9"/>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" s="134" t="s">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A21" s="137" t="s">
         <v>156</v>
       </c>
       <c r="B21" s="52" t="s">
@@ -5977,8 +6007,8 @@
       <c r="AE21" s="30"/>
       <c r="AF21" s="14"/>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A22" s="135"/>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A22" s="138"/>
       <c r="B22" s="52" t="s">
         <v>158</v>
       </c>
@@ -6051,8 +6081,8 @@
       <c r="AE22" s="30"/>
       <c r="AF22" s="14"/>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A23" s="135"/>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A23" s="138"/>
       <c r="B23" s="52" t="s">
         <v>159</v>
       </c>
@@ -6125,8 +6155,8 @@
       <c r="AE23" s="30"/>
       <c r="AF23" s="14"/>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A24" s="135"/>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A24" s="138"/>
       <c r="B24" s="52" t="s">
         <v>160</v>
       </c>
@@ -6199,8 +6229,8 @@
       <c r="AE24" s="30"/>
       <c r="AF24" s="14"/>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A25" s="135"/>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A25" s="138"/>
       <c r="B25" s="52" t="s">
         <v>161</v>
       </c>
@@ -6273,8 +6303,8 @@
       <c r="AE25" s="30"/>
       <c r="AF25" s="14"/>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A26" s="135"/>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A26" s="138"/>
       <c r="B26" s="52" t="s">
         <v>162</v>
       </c>
@@ -6347,8 +6377,8 @@
       <c r="AE26" s="30"/>
       <c r="AF26" s="14"/>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A27" s="135"/>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A27" s="138"/>
       <c r="B27" s="52" t="s">
         <v>163</v>
       </c>
@@ -6421,8 +6451,8 @@
       <c r="AE27" s="30"/>
       <c r="AF27" s="14"/>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A28" s="135"/>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A28" s="138"/>
       <c r="B28" s="52" t="s">
         <v>164</v>
       </c>
@@ -6495,8 +6525,8 @@
       <c r="AE28" s="30"/>
       <c r="AF28" s="14"/>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A29" s="135"/>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A29" s="138"/>
       <c r="B29" s="52" t="s">
         <v>165</v>
       </c>
@@ -6569,8 +6599,8 @@
       <c r="AE29" s="30"/>
       <c r="AF29" s="14"/>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A30" s="135"/>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A30" s="138"/>
       <c r="B30" s="52" t="s">
         <v>166</v>
       </c>
@@ -6643,8 +6673,8 @@
       <c r="AE30" s="30"/>
       <c r="AF30" s="14"/>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A31" s="135"/>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A31" s="138"/>
       <c r="B31" s="52" t="s">
         <v>167</v>
       </c>
@@ -6717,8 +6747,8 @@
       <c r="AE31" s="30"/>
       <c r="AF31" s="14"/>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A32" s="135"/>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A32" s="138"/>
       <c r="B32" s="52" t="s">
         <v>168</v>
       </c>
@@ -6792,7 +6822,7 @@
       <c r="AF32" s="14"/>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A33" s="136"/>
+      <c r="A33" s="139"/>
       <c r="B33" s="52" t="s">
         <v>169</v>
       </c>
@@ -6866,7 +6896,7 @@
       <c r="AF33" s="14"/>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A34" s="99"/>
+      <c r="A34" s="102"/>
       <c r="B34" s="52" t="s">
         <v>354</v>
       </c>
@@ -6938,7 +6968,7 @@
       <c r="AF34" s="14"/>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A35" s="99"/>
+      <c r="A35" s="102"/>
       <c r="B35" s="52" t="s">
         <v>355</v>
       </c>
@@ -7010,7 +7040,7 @@
       <c r="AF35" s="14"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="99"/>
+      <c r="A36" s="102"/>
       <c r="B36" s="52" t="s">
         <v>356</v>
       </c>
@@ -7082,7 +7112,7 @@
       <c r="AF36" s="14"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="99"/>
+      <c r="A37" s="102"/>
       <c r="B37" s="52" t="s">
         <v>357</v>
       </c>
@@ -7154,7 +7184,7 @@
       <c r="AF37" s="14"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
+      <c r="A38" s="102"/>
       <c r="B38" s="52" t="s">
         <v>358</v>
       </c>
@@ -7226,7 +7256,7 @@
       <c r="AF38" s="14"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A39" s="99"/>
+      <c r="A39" s="102"/>
       <c r="B39" s="52" t="s">
         <v>359</v>
       </c>
@@ -7298,7 +7328,7 @@
       <c r="AF39" s="14"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A40" s="99"/>
+      <c r="A40" s="102"/>
       <c r="B40" s="52" t="s">
         <v>360</v>
       </c>
@@ -7370,7 +7400,7 @@
       <c r="AF40" s="14"/>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A41" s="99"/>
+      <c r="A41" s="102"/>
       <c r="B41" s="52" t="s">
         <v>361</v>
       </c>
@@ -7672,11 +7702,11 @@
       <c r="AF44" s="14"/>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A45" s="76"/>
-      <c r="B45" s="77" t="s">
+      <c r="A45" s="79"/>
+      <c r="B45" s="80" t="s">
         <v>313</v>
       </c>
-      <c r="C45" s="78" t="s">
+      <c r="C45" s="81" t="s">
         <v>314</v>
       </c>
       <c r="D45" s="9">
@@ -7750,13 +7780,13 @@
       <c r="AF45" s="14"/>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A46" s="76" t="s">
+      <c r="A46" s="79" t="s">
         <v>312</v>
       </c>
-      <c r="B46" s="77" t="s">
+      <c r="B46" s="80" t="s">
         <v>313</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="82" t="s">
         <v>315</v>
       </c>
       <c r="D46" s="9">
@@ -7830,11 +7860,11 @@
       <c r="AF46" s="14"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A47" s="76"/>
-      <c r="B47" s="80" t="s">
+      <c r="A47" s="79"/>
+      <c r="B47" s="83" t="s">
         <v>313</v>
       </c>
-      <c r="C47" s="81" t="s">
+      <c r="C47" s="84" t="s">
         <v>316</v>
       </c>
       <c r="D47" s="9">
@@ -7906,11 +7936,11 @@
       <c r="AF47" s="14"/>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A48" s="82"/>
-      <c r="B48" s="77" t="s">
+      <c r="A48" s="85"/>
+      <c r="B48" s="80" t="s">
         <v>318</v>
       </c>
-      <c r="C48" s="84" t="s">
+      <c r="C48" s="87" t="s">
         <v>327</v>
       </c>
       <c r="D48" s="9">
@@ -7984,11 +8014,11 @@
       <c r="AF48" s="14"/>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A49" s="76"/>
+      <c r="A49" s="79"/>
       <c r="B49" s="73" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="85" t="s">
+      <c r="C49" s="88" t="s">
         <v>328</v>
       </c>
       <c r="D49" s="9">
@@ -8062,11 +8092,11 @@
       <c r="AF49" s="14"/>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A50" s="76"/>
-      <c r="B50" s="86" t="s">
+      <c r="A50" s="79"/>
+      <c r="B50" s="89" t="s">
         <v>320</v>
       </c>
-      <c r="C50" s="87" t="s">
+      <c r="C50" s="90" t="s">
         <v>329</v>
       </c>
       <c r="D50" s="9">
@@ -8140,11 +8170,11 @@
       <c r="AF50" s="14"/>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A51" s="76"/>
-      <c r="B51" s="88" t="s">
+      <c r="A51" s="79"/>
+      <c r="B51" s="91" t="s">
         <v>322</v>
       </c>
-      <c r="C51" s="89" t="s">
+      <c r="C51" s="92" t="s">
         <v>324</v>
       </c>
       <c r="D51" s="9">
@@ -8218,11 +8248,11 @@
       <c r="AF51" s="14"/>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A52" s="76"/>
-      <c r="B52" s="90" t="s">
+      <c r="A52" s="79"/>
+      <c r="B52" s="93" t="s">
         <v>321</v>
       </c>
-      <c r="C52" s="91" t="s">
+      <c r="C52" s="94" t="s">
         <v>325</v>
       </c>
       <c r="D52" s="9">
@@ -8294,11 +8324,11 @@
       <c r="AF52" s="14"/>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A53" s="83"/>
-      <c r="B53" s="92" t="s">
+      <c r="A53" s="86"/>
+      <c r="B53" s="95" t="s">
         <v>323</v>
       </c>
-      <c r="C53" s="93" t="s">
+      <c r="C53" s="96" t="s">
         <v>326</v>
       </c>
       <c r="D53" s="9">
@@ -8370,11 +8400,11 @@
       <c r="AF53" s="14"/>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A54" s="76"/>
-      <c r="B54" s="97" t="s">
+      <c r="A54" s="79"/>
+      <c r="B54" s="100" t="s">
         <v>335</v>
       </c>
-      <c r="C54" s="98" t="s">
+      <c r="C54" s="101" t="s">
         <v>336</v>
       </c>
       <c r="D54" s="9">
@@ -8446,11 +8476,11 @@
       <c r="AF54" s="14"/>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A55" s="76"/>
-      <c r="B55" s="77" t="s">
+      <c r="A55" s="79"/>
+      <c r="B55" s="80" t="s">
         <v>337</v>
       </c>
-      <c r="C55" s="84"/>
+      <c r="C55" s="87"/>
       <c r="D55" s="9">
         <v>501</v>
       </c>
@@ -8479,7 +8509,7 @@
         <v>101</v>
       </c>
       <c r="O55" s="9"/>
-      <c r="P55" s="101">
+      <c r="P55" s="104">
         <v>22009</v>
       </c>
       <c r="Q55" s="9">
@@ -8522,11 +8552,11 @@
       <c r="AF55" s="14"/>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A56" s="76"/>
-      <c r="B56" s="77" t="s">
+      <c r="A56" s="79"/>
+      <c r="B56" s="80" t="s">
         <v>338</v>
       </c>
-      <c r="C56" s="84"/>
+      <c r="C56" s="87"/>
       <c r="D56" s="9">
         <v>502</v>
       </c>
@@ -8555,7 +8585,7 @@
         <v>101</v>
       </c>
       <c r="O56" s="9"/>
-      <c r="P56" s="101">
+      <c r="P56" s="104">
         <v>22009</v>
       </c>
       <c r="Q56" s="9">
@@ -8598,11 +8628,11 @@
       <c r="AF56" s="14"/>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A57" s="76"/>
-      <c r="B57" s="77" t="s">
+      <c r="A57" s="79"/>
+      <c r="B57" s="80" t="s">
         <v>339</v>
       </c>
-      <c r="C57" s="84"/>
+      <c r="C57" s="87"/>
       <c r="D57" s="9">
         <v>503</v>
       </c>
@@ -8631,7 +8661,7 @@
         <v>101</v>
       </c>
       <c r="O57" s="9"/>
-      <c r="P57" s="101">
+      <c r="P57" s="104">
         <v>22009</v>
       </c>
       <c r="Q57" s="9">
@@ -8674,11 +8704,11 @@
       <c r="AF57" s="14"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A58" s="76"/>
-      <c r="B58" s="77" t="s">
+      <c r="A58" s="79"/>
+      <c r="B58" s="80" t="s">
         <v>340</v>
       </c>
-      <c r="C58" s="84"/>
+      <c r="C58" s="87"/>
       <c r="D58" s="9">
         <v>504</v>
       </c>
@@ -8707,7 +8737,7 @@
         <v>101</v>
       </c>
       <c r="O58" s="9"/>
-      <c r="P58" s="101">
+      <c r="P58" s="104">
         <v>22009</v>
       </c>
       <c r="Q58" s="9">
@@ -8750,11 +8780,11 @@
       <c r="AF58" s="14"/>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A59" s="76"/>
-      <c r="B59" s="77" t="s">
+      <c r="A59" s="79"/>
+      <c r="B59" s="80" t="s">
         <v>341</v>
       </c>
-      <c r="C59" s="84"/>
+      <c r="C59" s="87"/>
       <c r="D59" s="9">
         <v>505</v>
       </c>
@@ -8783,7 +8813,7 @@
         <v>101</v>
       </c>
       <c r="O59" s="9"/>
-      <c r="P59" s="101">
+      <c r="P59" s="104">
         <v>22009</v>
       </c>
       <c r="Q59" s="9">
@@ -8826,11 +8856,11 @@
       <c r="AF59" s="14"/>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A60" s="76"/>
-      <c r="B60" s="77" t="s">
+      <c r="A60" s="79"/>
+      <c r="B60" s="80" t="s">
         <v>342</v>
       </c>
-      <c r="C60" s="84"/>
+      <c r="C60" s="87"/>
       <c r="D60" s="9">
         <v>506</v>
       </c>
@@ -8859,7 +8889,7 @@
         <v>101</v>
       </c>
       <c r="O60" s="9"/>
-      <c r="P60" s="101">
+      <c r="P60" s="104">
         <v>22009</v>
       </c>
       <c r="Q60" s="9">
@@ -8902,11 +8932,11 @@
       <c r="AF60" s="14"/>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A61" s="76"/>
-      <c r="B61" s="77" t="s">
+      <c r="A61" s="79"/>
+      <c r="B61" s="80" t="s">
         <v>343</v>
       </c>
-      <c r="C61" s="84"/>
+      <c r="C61" s="87"/>
       <c r="D61" s="9">
         <v>507</v>
       </c>
@@ -8935,7 +8965,7 @@
         <v>101</v>
       </c>
       <c r="O61" s="9"/>
-      <c r="P61" s="101">
+      <c r="P61" s="104">
         <v>22009</v>
       </c>
       <c r="Q61" s="9">
@@ -8978,11 +9008,11 @@
       <c r="AF61" s="14"/>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A62" s="76"/>
-      <c r="B62" s="77" t="s">
+      <c r="A62" s="79"/>
+      <c r="B62" s="80" t="s">
         <v>344</v>
       </c>
-      <c r="C62" s="84"/>
+      <c r="C62" s="87"/>
       <c r="D62" s="9">
         <v>508</v>
       </c>
@@ -9011,7 +9041,7 @@
         <v>101</v>
       </c>
       <c r="O62" s="9"/>
-      <c r="P62" s="101">
+      <c r="P62" s="104">
         <v>22009</v>
       </c>
       <c r="Q62" s="9">
@@ -9054,11 +9084,11 @@
       <c r="AF62" s="14"/>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A63" s="76"/>
-      <c r="B63" s="77" t="s">
+      <c r="A63" s="79"/>
+      <c r="B63" s="80" t="s">
         <v>345</v>
       </c>
-      <c r="C63" s="84"/>
+      <c r="C63" s="87"/>
       <c r="D63" s="9">
         <v>509</v>
       </c>
@@ -9087,7 +9117,7 @@
         <v>101</v>
       </c>
       <c r="O63" s="9"/>
-      <c r="P63" s="101">
+      <c r="P63" s="104">
         <v>22009</v>
       </c>
       <c r="Q63" s="9">
@@ -9130,11 +9160,11 @@
       <c r="AF63" s="14"/>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A64" s="76"/>
-      <c r="B64" s="77" t="s">
+      <c r="A64" s="79"/>
+      <c r="B64" s="80" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="84"/>
+      <c r="C64" s="87"/>
       <c r="D64" s="9">
         <v>510</v>
       </c>
@@ -9163,7 +9193,7 @@
         <v>101</v>
       </c>
       <c r="O64" s="9"/>
-      <c r="P64" s="101">
+      <c r="P64" s="104">
         <v>22009</v>
       </c>
       <c r="Q64" s="9">
@@ -9205,12 +9235,12 @@
       <c r="AE64" s="30"/>
       <c r="AF64" s="14"/>
     </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A65" s="76"/>
-      <c r="B65" s="77" t="s">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A65" s="79"/>
+      <c r="B65" s="80" t="s">
         <v>347</v>
       </c>
-      <c r="C65" s="84"/>
+      <c r="C65" s="87"/>
       <c r="D65" s="9">
         <v>511</v>
       </c>
@@ -9239,7 +9269,7 @@
         <v>101</v>
       </c>
       <c r="O65" s="9"/>
-      <c r="P65" s="101">
+      <c r="P65" s="104">
         <v>22009</v>
       </c>
       <c r="Q65" s="9">
@@ -9281,12 +9311,12 @@
       <c r="AE65" s="30"/>
       <c r="AF65" s="14"/>
     </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A66" s="76"/>
-      <c r="B66" s="77" t="s">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A66" s="79"/>
+      <c r="B66" s="80" t="s">
         <v>348</v>
       </c>
-      <c r="C66" s="84"/>
+      <c r="C66" s="87"/>
       <c r="D66" s="9">
         <v>512</v>
       </c>
@@ -9315,7 +9345,7 @@
         <v>101</v>
       </c>
       <c r="O66" s="9"/>
-      <c r="P66" s="101">
+      <c r="P66" s="104">
         <v>22009</v>
       </c>
       <c r="Q66" s="9">
@@ -9357,12 +9387,12 @@
       <c r="AE66" s="30"/>
       <c r="AF66" s="14"/>
     </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A67" s="76"/>
-      <c r="B67" s="77" t="s">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A67" s="79"/>
+      <c r="B67" s="80" t="s">
         <v>349</v>
       </c>
-      <c r="C67" s="84"/>
+      <c r="C67" s="87"/>
       <c r="D67" s="9">
         <v>513</v>
       </c>
@@ -9391,7 +9421,7 @@
         <v>101</v>
       </c>
       <c r="O67" s="9"/>
-      <c r="P67" s="101">
+      <c r="P67" s="104">
         <v>22009</v>
       </c>
       <c r="Q67" s="9">
@@ -9433,12 +9463,12 @@
       <c r="AE67" s="30"/>
       <c r="AF67" s="14"/>
     </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A68" s="76"/>
-      <c r="B68" s="77" t="s">
+    <row r="68" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A68" s="79"/>
+      <c r="B68" s="80" t="s">
         <v>350</v>
       </c>
-      <c r="C68" s="84"/>
+      <c r="C68" s="87"/>
       <c r="D68" s="9">
         <v>514</v>
       </c>
@@ -9467,7 +9497,7 @@
         <v>101</v>
       </c>
       <c r="O68" s="9"/>
-      <c r="P68" s="101">
+      <c r="P68" s="104">
         <v>22009</v>
       </c>
       <c r="Q68" s="9">
@@ -9509,12 +9539,12 @@
       <c r="AE68" s="30"/>
       <c r="AF68" s="14"/>
     </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A69" s="76"/>
-      <c r="B69" s="77" t="s">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A69" s="79"/>
+      <c r="B69" s="80" t="s">
         <v>351</v>
       </c>
-      <c r="C69" s="84"/>
+      <c r="C69" s="87"/>
       <c r="D69" s="9">
         <v>515</v>
       </c>
@@ -9543,7 +9573,7 @@
         <v>101</v>
       </c>
       <c r="O69" s="9"/>
-      <c r="P69" s="101">
+      <c r="P69" s="104">
         <v>22009</v>
       </c>
       <c r="Q69" s="9">
@@ -9585,8 +9615,8 @@
       <c r="AE69" s="30"/>
       <c r="AF69" s="14"/>
     </row>
-    <row r="70" spans="1:37" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="124" t="s">
+    <row r="70" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="127" t="s">
         <v>82</v>
       </c>
       <c r="B70" s="47" t="s">
@@ -9672,8 +9702,8 @@
         <v>90041</v>
       </c>
     </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A71" s="125"/>
+    <row r="71" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A71" s="128"/>
       <c r="B71" s="34" t="s">
         <v>78</v>
       </c>
@@ -9757,8 +9787,8 @@
         <v>10153</v>
       </c>
     </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A72" s="125"/>
+    <row r="72" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A72" s="128"/>
       <c r="B72" s="34" t="s">
         <v>79</v>
       </c>
@@ -9839,8 +9869,8 @@
         <v>10256</v>
       </c>
     </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A73" s="125"/>
+    <row r="73" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A73" s="128"/>
       <c r="B73" s="34" t="s">
         <v>80</v>
       </c>
@@ -9873,7 +9903,7 @@
         <v>84</v>
       </c>
       <c r="O73" s="9"/>
-      <c r="P73" s="101">
+      <c r="P73" s="104">
         <v>22009</v>
       </c>
       <c r="Q73" s="9">
@@ -9912,9 +9942,12 @@
       <c r="AD73" s="30"/>
       <c r="AE73" s="30"/>
       <c r="AF73" s="14"/>
+      <c r="AM73" s="76">
+        <v>90009</v>
+      </c>
     </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A74" s="125"/>
+    <row r="74" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A74" s="128"/>
       <c r="B74" s="43" t="s">
         <v>81</v>
       </c>
@@ -9998,7 +10031,7 @@
         <v>10157</v>
       </c>
     </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A75" s="60"/>
       <c r="B75" s="43" t="s">
         <v>185</v>
@@ -10032,7 +10065,7 @@
         <v>84</v>
       </c>
       <c r="O75" s="9"/>
-      <c r="P75" s="101">
+      <c r="P75" s="104">
         <v>22009</v>
       </c>
       <c r="Q75" s="9">
@@ -10078,8 +10111,8 @@
       </c>
       <c r="AJ75" s="71"/>
     </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A76" s="124" t="s">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A76" s="127" t="s">
         <v>89</v>
       </c>
       <c r="B76" s="34" t="s">
@@ -10165,8 +10198,8 @@
         <v>10252</v>
       </c>
     </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A77" s="125"/>
+    <row r="77" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A77" s="128"/>
       <c r="B77" s="34" t="s">
         <v>86</v>
       </c>
@@ -10250,8 +10283,8 @@
         <v>10252</v>
       </c>
     </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A78" s="125"/>
+    <row r="78" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A78" s="128"/>
       <c r="B78" s="34" t="s">
         <v>87</v>
       </c>
@@ -10306,7 +10339,7 @@
         <v>1</v>
       </c>
       <c r="U78" s="9">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="V78" s="9"/>
       <c r="W78" s="57">
@@ -10330,8 +10363,8 @@
       <c r="AE78" s="30"/>
       <c r="AF78" s="14"/>
     </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A79" s="125"/>
+    <row r="79" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A79" s="128"/>
       <c r="B79" s="34" t="s">
         <v>88</v>
       </c>
@@ -10364,7 +10397,7 @@
         <v>84</v>
       </c>
       <c r="O79" s="9"/>
-      <c r="P79" s="101">
+      <c r="P79" s="104">
         <v>22009</v>
       </c>
       <c r="Q79" s="9">
@@ -10403,9 +10436,12 @@
       <c r="AD79" s="30"/>
       <c r="AE79" s="30"/>
       <c r="AF79" s="14"/>
+      <c r="AM79" s="77">
+        <v>10255</v>
+      </c>
     </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A80" s="125"/>
+    <row r="80" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A80" s="128"/>
       <c r="B80" s="47" t="s">
         <v>90</v>
       </c>
@@ -10489,8 +10525,8 @@
         <v>90042</v>
       </c>
     </row>
-    <row r="81" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A81" s="126"/>
+    <row r="81" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A81" s="129"/>
       <c r="B81" s="34" t="s">
         <v>91</v>
       </c>
@@ -10542,14 +10578,12 @@
         <v>1</v>
       </c>
       <c r="T81" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" s="9">
-        <v>10</v>
-      </c>
-      <c r="V81" s="9">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="V81" s="9"/>
       <c r="W81" s="57">
         <v>6011</v>
       </c>
@@ -10570,18 +10604,9 @@
       <c r="AD81" s="30"/>
       <c r="AE81" s="30"/>
       <c r="AF81" s="14"/>
-      <c r="AH81" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ81" s="2">
-        <v>10257</v>
-      </c>
-      <c r="AK81" s="2">
-        <v>10257</v>
-      </c>
     </row>
-    <row r="82" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A82" s="124" t="s">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A82" s="127" t="s">
         <v>92</v>
       </c>
       <c r="B82" s="34" t="s">
@@ -10667,8 +10692,8 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="83" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A83" s="125"/>
+    <row r="83" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A83" s="128"/>
       <c r="B83" s="34" t="s">
         <v>94</v>
       </c>
@@ -10752,8 +10777,8 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="84" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A84" s="125"/>
+    <row r="84" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A84" s="128"/>
       <c r="B84" s="34" t="s">
         <v>96</v>
       </c>
@@ -10805,14 +10830,12 @@
         <v>1</v>
       </c>
       <c r="T84" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U84" s="9">
-        <v>10</v>
-      </c>
-      <c r="V84" s="9">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="V84" s="9"/>
       <c r="W84" s="57">
         <v>6014</v>
       </c>
@@ -10833,12 +10856,9 @@
       <c r="AD84" s="30"/>
       <c r="AE84" s="30"/>
       <c r="AF84" s="14"/>
-      <c r="AH84" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="85" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A85" s="125"/>
+    <row r="85" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A85" s="128"/>
       <c r="B85" s="58" t="s">
         <v>97</v>
       </c>
@@ -10918,8 +10938,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A86" s="125"/>
+    <row r="86" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A86" s="128"/>
       <c r="B86" s="34" t="s">
         <v>98</v>
       </c>
@@ -10952,7 +10972,7 @@
         <v>84</v>
       </c>
       <c r="O86" s="9"/>
-      <c r="P86" s="101">
+      <c r="P86" s="104">
         <v>22009</v>
       </c>
       <c r="Q86" s="9">
@@ -10991,9 +11011,12 @@
       <c r="AD86" s="30"/>
       <c r="AE86" s="30"/>
       <c r="AF86" s="14"/>
+      <c r="AM86" s="78">
+        <v>10355</v>
+      </c>
     </row>
-    <row r="87" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A87" s="125"/>
+    <row r="87" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A87" s="128"/>
       <c r="B87" s="47" t="s">
         <v>99</v>
       </c>
@@ -11077,8 +11100,8 @@
         <v>90043</v>
       </c>
     </row>
-    <row r="88" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A88" s="126"/>
+    <row r="88" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A88" s="129"/>
       <c r="B88" s="34" t="s">
         <v>100</v>
       </c>
@@ -11111,7 +11134,7 @@
         <v>84</v>
       </c>
       <c r="O88" s="9"/>
-      <c r="P88" s="101">
+      <c r="P88" s="104">
         <v>22009</v>
       </c>
       <c r="Q88" s="9">
@@ -11150,9 +11173,12 @@
       <c r="AD88" s="30"/>
       <c r="AE88" s="30"/>
       <c r="AF88" s="14"/>
+      <c r="AM88" s="78">
+        <v>10355</v>
+      </c>
     </row>
-    <row r="89" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A89" s="124" t="s">
+    <row r="89" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A89" s="127" t="s">
         <v>102</v>
       </c>
       <c r="B89" s="34" t="s">
@@ -11187,7 +11213,7 @@
         <v>84</v>
       </c>
       <c r="O89" s="9"/>
-      <c r="P89" s="101">
+      <c r="P89" s="104">
         <v>22009</v>
       </c>
       <c r="Q89" s="9">
@@ -11229,9 +11255,12 @@
       <c r="AH89" s="2">
         <v>1</v>
       </c>
+      <c r="AM89" s="77">
+        <v>10451</v>
+      </c>
     </row>
-    <row r="90" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A90" s="125"/>
+    <row r="90" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A90" s="128"/>
       <c r="B90" s="34" t="s">
         <v>112</v>
       </c>
@@ -11264,7 +11293,7 @@
         <v>84</v>
       </c>
       <c r="O90" s="9"/>
-      <c r="P90" s="101">
+      <c r="P90" s="104">
         <v>22009</v>
       </c>
       <c r="Q90" s="9">
@@ -11306,9 +11335,12 @@
       <c r="AH90" s="2">
         <v>1</v>
       </c>
+      <c r="AM90" s="78">
+        <v>10451</v>
+      </c>
     </row>
-    <row r="91" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A91" s="125"/>
+    <row r="91" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A91" s="128"/>
       <c r="B91" s="34" t="s">
         <v>113</v>
       </c>
@@ -11341,7 +11373,7 @@
         <v>84</v>
       </c>
       <c r="O91" s="9"/>
-      <c r="P91" s="101">
+      <c r="P91" s="104">
         <v>22009</v>
       </c>
       <c r="Q91" s="9">
@@ -11383,9 +11415,12 @@
       <c r="AH91" s="2">
         <v>1</v>
       </c>
+      <c r="AM91" s="77">
+        <v>10451</v>
+      </c>
     </row>
-    <row r="92" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A92" s="125"/>
+    <row r="92" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A92" s="128"/>
       <c r="B92" s="34" t="s">
         <v>103</v>
       </c>
@@ -11437,14 +11472,12 @@
         <v>1</v>
       </c>
       <c r="T92" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U92" s="9">
-        <v>10</v>
-      </c>
-      <c r="V92" s="9">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="V92" s="9"/>
       <c r="W92" s="57">
         <v>6022</v>
       </c>
@@ -11465,12 +11498,9 @@
       <c r="AD92" s="30"/>
       <c r="AE92" s="30"/>
       <c r="AF92" s="14"/>
-      <c r="AH92" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="93" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A93" s="125"/>
+    <row r="93" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A93" s="128"/>
       <c r="B93" s="34" t="s">
         <v>105</v>
       </c>
@@ -11554,8 +11584,8 @@
         <v>10452</v>
       </c>
     </row>
-    <row r="94" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A94" s="125"/>
+    <row r="94" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A94" s="128"/>
       <c r="B94" s="34" t="s">
         <v>106</v>
       </c>
@@ -11639,8 +11669,8 @@
         <v>10452</v>
       </c>
     </row>
-    <row r="95" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A95" s="125"/>
+    <row r="95" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A95" s="128"/>
       <c r="B95" s="34" t="s">
         <v>107</v>
       </c>
@@ -11724,8 +11754,8 @@
         <v>10455</v>
       </c>
     </row>
-    <row r="96" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A96" s="125"/>
+    <row r="96" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A96" s="128"/>
       <c r="B96" s="34" t="s">
         <v>108</v>
       </c>
@@ -11758,7 +11788,7 @@
         <v>84</v>
       </c>
       <c r="O96" s="9"/>
-      <c r="P96" s="101">
+      <c r="P96" s="104">
         <v>22009</v>
       </c>
       <c r="Q96" s="9">
@@ -11800,9 +11830,12 @@
       <c r="AH96" s="2">
         <v>1</v>
       </c>
+      <c r="AM96" s="78">
+        <v>10456</v>
+      </c>
     </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A97" s="125"/>
+    <row r="97" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A97" s="128"/>
       <c r="B97" s="34" t="s">
         <v>109</v>
       </c>
@@ -11886,7 +11919,7 @@
         <v>10456</v>
       </c>
     </row>
-    <row r="98" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A98" s="45"/>
       <c r="B98" s="47" t="s">
         <v>110</v>
@@ -11971,8 +12004,8 @@
         <v>90044</v>
       </c>
     </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A99" s="124" t="s">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A99" s="127" t="s">
         <v>121</v>
       </c>
       <c r="B99" s="34" t="s">
@@ -12058,8 +12091,8 @@
         <v>10552</v>
       </c>
     </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A100" s="125"/>
+    <row r="100" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A100" s="128"/>
       <c r="B100" s="34" t="s">
         <v>116</v>
       </c>
@@ -12143,8 +12176,8 @@
         <v>10552</v>
       </c>
     </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A101" s="125"/>
+    <row r="101" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A101" s="128"/>
       <c r="B101" s="34" t="s">
         <v>117</v>
       </c>
@@ -12177,7 +12210,7 @@
         <v>84</v>
       </c>
       <c r="O101" s="9"/>
-      <c r="P101" s="101">
+      <c r="P101" s="104">
         <v>22009</v>
       </c>
       <c r="Q101" s="9">
@@ -12216,9 +12249,12 @@
       <c r="AD101" s="30"/>
       <c r="AE101" s="30"/>
       <c r="AF101" s="14"/>
+      <c r="AM101" s="77">
+        <v>10554</v>
+      </c>
     </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A102" s="125"/>
+    <row r="102" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A102" s="128"/>
       <c r="B102" s="34" t="s">
         <v>118</v>
       </c>
@@ -12251,7 +12287,7 @@
         <v>84</v>
       </c>
       <c r="O102" s="9"/>
-      <c r="P102" s="101">
+      <c r="P102" s="104">
         <v>22009</v>
       </c>
       <c r="Q102" s="9">
@@ -12290,9 +12326,12 @@
       <c r="AD102" s="30"/>
       <c r="AE102" s="30"/>
       <c r="AF102" s="14"/>
+      <c r="AM102" s="78">
+        <v>10555</v>
+      </c>
     </row>
-    <row r="103" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A103" s="125"/>
+    <row r="103" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A103" s="128"/>
       <c r="B103" s="34" t="s">
         <v>119</v>
       </c>
@@ -12325,7 +12364,7 @@
         <v>84</v>
       </c>
       <c r="O103" s="9"/>
-      <c r="P103" s="101">
+      <c r="P103" s="104">
         <v>22009</v>
       </c>
       <c r="Q103" s="9">
@@ -12364,9 +12403,12 @@
       <c r="AD103" s="30"/>
       <c r="AE103" s="30"/>
       <c r="AF103" s="14"/>
+      <c r="AM103" s="77">
+        <v>10555</v>
+      </c>
     </row>
-    <row r="104" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A104" s="125"/>
+    <row r="104" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A104" s="128"/>
       <c r="B104" s="34" t="s">
         <v>120</v>
       </c>
@@ -12450,8 +12492,8 @@
         <v>10556</v>
       </c>
     </row>
-    <row r="105" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A105" s="125"/>
+    <row r="105" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A105" s="128"/>
       <c r="B105" s="47" t="s">
         <v>122</v>
       </c>
@@ -12535,8 +12577,8 @@
         <v>90045</v>
       </c>
     </row>
-    <row r="106" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A106" s="125"/>
+    <row r="106" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A106" s="128"/>
       <c r="B106" s="34" t="s">
         <v>123</v>
       </c>
@@ -12614,8 +12656,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A107" s="126"/>
+    <row r="107" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A107" s="129"/>
       <c r="B107" s="34" t="s">
         <v>177</v>
       </c>
@@ -12648,7 +12690,7 @@
         <v>84</v>
       </c>
       <c r="O107" s="9"/>
-      <c r="P107" s="101">
+      <c r="P107" s="104">
         <v>22009</v>
       </c>
       <c r="Q107" s="9">
@@ -12691,8 +12733,8 @@
         <v>10552</v>
       </c>
     </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A108" s="118" t="s">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A108" s="121" t="s">
         <v>124</v>
       </c>
       <c r="B108" s="59" t="s">
@@ -12772,8 +12814,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A109" s="119"/>
+    <row r="109" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A109" s="122"/>
       <c r="B109" s="59" t="s">
         <v>126</v>
       </c>
@@ -12825,14 +12867,12 @@
         <v>1</v>
       </c>
       <c r="T109" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U109" s="9">
-        <v>10</v>
-      </c>
-      <c r="V109" s="9">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="V109" s="9"/>
       <c r="W109" s="57">
         <v>6038</v>
       </c>
@@ -12853,12 +12893,9 @@
       <c r="AD109" s="30"/>
       <c r="AE109" s="30"/>
       <c r="AF109" s="14"/>
-      <c r="AH109" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A110" s="119"/>
+    <row r="110" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A110" s="122"/>
       <c r="B110" s="59" t="s">
         <v>127</v>
       </c>
@@ -12936,8 +12973,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A111" s="119"/>
+    <row r="111" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A111" s="122"/>
       <c r="B111" s="59" t="s">
         <v>141</v>
       </c>
@@ -13018,8 +13055,8 @@
         <v>10282</v>
       </c>
     </row>
-    <row r="112" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A112" s="119"/>
+    <row r="112" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A112" s="122"/>
       <c r="B112" s="68" t="s">
         <v>128</v>
       </c>
@@ -13101,7 +13138,7 @@
       </c>
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A113" s="119"/>
+      <c r="A113" s="122"/>
       <c r="B113" s="59" t="s">
         <v>129</v>
       </c>
@@ -13183,7 +13220,7 @@
       </c>
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A114" s="119"/>
+      <c r="A114" s="122"/>
       <c r="B114" s="59" t="s">
         <v>130</v>
       </c>
@@ -13265,7 +13302,7 @@
       </c>
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A115" s="119"/>
+      <c r="A115" s="122"/>
       <c r="B115" s="59" t="s">
         <v>131</v>
       </c>
@@ -13347,7 +13384,7 @@
       </c>
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A116" s="119"/>
+      <c r="A116" s="122"/>
       <c r="B116" s="59" t="s">
         <v>132</v>
       </c>
@@ -13429,7 +13466,7 @@
       </c>
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A117" s="119"/>
+      <c r="A117" s="122"/>
       <c r="B117" s="59" t="s">
         <v>133</v>
       </c>
@@ -13511,7 +13548,7 @@
       </c>
     </row>
     <row r="118" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A118" s="119"/>
+      <c r="A118" s="122"/>
       <c r="B118" s="59" t="s">
         <v>134</v>
       </c>
@@ -13593,7 +13630,7 @@
       </c>
     </row>
     <row r="119" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A119" s="119"/>
+      <c r="A119" s="122"/>
       <c r="B119" s="59" t="s">
         <v>135</v>
       </c>
@@ -13675,7 +13712,7 @@
       </c>
     </row>
     <row r="120" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A120" s="119"/>
+      <c r="A120" s="122"/>
       <c r="B120" s="59" t="s">
         <v>136</v>
       </c>
@@ -13754,7 +13791,7 @@
       </c>
     </row>
     <row r="121" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A121" s="119"/>
+      <c r="A121" s="122"/>
       <c r="B121" s="59" t="s">
         <v>137</v>
       </c>
@@ -13836,7 +13873,7 @@
       </c>
     </row>
     <row r="122" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A122" s="119"/>
+      <c r="A122" s="122"/>
       <c r="B122" s="59" t="s">
         <v>138</v>
       </c>
@@ -13918,7 +13955,7 @@
       </c>
     </row>
     <row r="123" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A123" s="119"/>
+      <c r="A123" s="122"/>
       <c r="B123" s="59" t="s">
         <v>139</v>
       </c>
@@ -14000,7 +14037,7 @@
       </c>
     </row>
     <row r="124" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A124" s="120"/>
+      <c r="A124" s="123"/>
       <c r="B124" s="59" t="s">
         <v>140</v>
       </c>
@@ -14079,7 +14116,7 @@
       </c>
     </row>
     <row r="125" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A125" s="115" t="s">
+      <c r="A125" s="118" t="s">
         <v>144</v>
       </c>
       <c r="B125" s="50" t="s">
@@ -14157,7 +14194,7 @@
       <c r="AF125" s="14"/>
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A126" s="116"/>
+      <c r="A126" s="119"/>
       <c r="B126" s="50" t="s">
         <v>146</v>
       </c>
@@ -14236,7 +14273,7 @@
       </c>
     </row>
     <row r="127" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A127" s="116"/>
+      <c r="A127" s="119"/>
       <c r="B127" s="50" t="s">
         <v>147</v>
       </c>
@@ -14315,7 +14352,7 @@
       </c>
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A128" s="116"/>
+      <c r="A128" s="119"/>
       <c r="B128" s="50" t="s">
         <v>148</v>
       </c>
@@ -14348,7 +14385,7 @@
         <v>84</v>
       </c>
       <c r="O128" s="9"/>
-      <c r="P128" s="101">
+      <c r="P128" s="104">
         <v>22009</v>
       </c>
       <c r="Q128" s="9">
@@ -14390,8 +14427,8 @@
       <c r="AE128" s="30"/>
       <c r="AF128" s="14"/>
     </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A129" s="116"/>
+    <row r="129" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A129" s="119"/>
       <c r="B129" s="50" t="s">
         <v>149</v>
       </c>
@@ -14424,7 +14461,7 @@
         <v>84</v>
       </c>
       <c r="O129" s="9"/>
-      <c r="P129" s="101">
+      <c r="P129" s="104">
         <v>22009</v>
       </c>
       <c r="Q129" s="9">
@@ -14466,8 +14503,8 @@
       <c r="AE129" s="30"/>
       <c r="AF129" s="14"/>
     </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A130" s="116"/>
+    <row r="130" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A130" s="119"/>
       <c r="B130" s="50" t="s">
         <v>150</v>
       </c>
@@ -14544,8 +14581,8 @@
       <c r="AE130" s="30"/>
       <c r="AF130" s="14"/>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A131" s="116"/>
+    <row r="131" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A131" s="119"/>
       <c r="B131" s="50" t="s">
         <v>151</v>
       </c>
@@ -14578,7 +14615,7 @@
         <v>84</v>
       </c>
       <c r="O131" s="9"/>
-      <c r="P131" s="101">
+      <c r="P131" s="104">
         <v>22009</v>
       </c>
       <c r="Q131" s="9">
@@ -14617,9 +14654,12 @@
       <c r="AD131" s="30"/>
       <c r="AE131" s="30"/>
       <c r="AF131" s="14"/>
+      <c r="AM131" s="77">
+        <v>10907</v>
+      </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A132" s="117"/>
+    <row r="132" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A132" s="120"/>
       <c r="B132" s="50" t="s">
         <v>152</v>
       </c>
@@ -14671,14 +14711,12 @@
         <v>1</v>
       </c>
       <c r="T132" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U132" s="9">
-        <v>10</v>
-      </c>
-      <c r="V132" s="9">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="V132" s="9"/>
       <c r="W132" s="57">
         <v>6061</v>
       </c>
@@ -14699,12 +14737,9 @@
       <c r="AD132" s="30"/>
       <c r="AE132" s="30"/>
       <c r="AF132" s="14"/>
-      <c r="AH132" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="133" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="113" t="s">
+    <row r="133" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="116" t="s">
         <v>186</v>
       </c>
       <c r="B133" s="61" t="s">
@@ -14789,8 +14824,8 @@
         <v>90101</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A134" s="114"/>
+    <row r="134" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A134" s="117"/>
       <c r="B134" s="61" t="s">
         <v>188</v>
       </c>
@@ -14873,8 +14908,8 @@
         <v>90102</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A135" s="114"/>
+    <row r="135" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A135" s="117"/>
       <c r="B135" s="61" t="s">
         <v>189</v>
       </c>
@@ -14957,8 +14992,8 @@
         <v>90103</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A136" s="114"/>
+    <row r="136" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A136" s="117"/>
       <c r="B136" s="61" t="s">
         <v>190</v>
       </c>
@@ -15041,8 +15076,8 @@
         <v>90104</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A137" s="114"/>
+    <row r="137" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A137" s="117"/>
       <c r="B137" s="61" t="s">
         <v>191</v>
       </c>
@@ -15125,8 +15160,8 @@
         <v>90105</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A138" s="114"/>
+    <row r="138" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A138" s="117"/>
       <c r="B138" s="61" t="s">
         <v>192</v>
       </c>
@@ -15209,8 +15244,8 @@
         <v>90106</v>
       </c>
     </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A139" s="114"/>
+    <row r="139" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A139" s="117"/>
       <c r="B139" s="61" t="s">
         <v>193</v>
       </c>
@@ -15293,8 +15328,8 @@
         <v>90107</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A140" s="114"/>
+    <row r="140" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A140" s="117"/>
       <c r="B140" s="61" t="s">
         <v>194</v>
       </c>
@@ -15377,7 +15412,7 @@
         <v>90108</v>
       </c>
     </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A141" s="63"/>
       <c r="B141" s="61" t="s">
         <v>211</v>
@@ -15453,8 +15488,8 @@
       <c r="AE141" s="30"/>
       <c r="AF141" s="14"/>
     </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A142" s="112" t="s">
+    <row r="142" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A142" s="115" t="s">
         <v>213</v>
       </c>
       <c r="B142" s="61" t="s">
@@ -15531,8 +15566,8 @@
       <c r="AE142" s="30"/>
       <c r="AF142" s="14"/>
     </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A143" s="112"/>
+    <row r="143" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A143" s="115"/>
       <c r="B143" s="61" t="s">
         <v>215</v>
       </c>
@@ -15607,8 +15642,8 @@
       <c r="AE143" s="30"/>
       <c r="AF143" s="14"/>
     </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A144" s="112"/>
+    <row r="144" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A144" s="115"/>
       <c r="B144" s="61" t="s">
         <v>216</v>
       </c>
@@ -15684,7 +15719,7 @@
       <c r="AF144" s="14"/>
     </row>
     <row r="145" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A145" s="112"/>
+      <c r="A145" s="115"/>
       <c r="B145" s="61" t="s">
         <v>217</v>
       </c>
@@ -15760,7 +15795,7 @@
       <c r="AF145" s="14"/>
     </row>
     <row r="146" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A146" s="112"/>
+      <c r="A146" s="115"/>
       <c r="B146" s="61" t="s">
         <v>218</v>
       </c>
@@ -15836,7 +15871,7 @@
       <c r="AF146" s="14"/>
     </row>
     <row r="147" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A147" s="112"/>
+      <c r="A147" s="115"/>
       <c r="B147" s="61" t="s">
         <v>219</v>
       </c>
@@ -15912,7 +15947,7 @@
       <c r="AF147" s="14"/>
     </row>
     <row r="148" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A148" s="112"/>
+      <c r="A148" s="115"/>
       <c r="B148" s="61" t="s">
         <v>220</v>
       </c>
@@ -15988,7 +16023,7 @@
       <c r="AF148" s="14"/>
     </row>
     <row r="149" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A149" s="112"/>
+      <c r="A149" s="115"/>
       <c r="B149" s="61" t="s">
         <v>221</v>
       </c>
@@ -16176,7 +16211,7 @@
         <v>84</v>
       </c>
       <c r="O151" s="9"/>
-      <c r="P151" s="101">
+      <c r="P151" s="104">
         <v>22009</v>
       </c>
       <c r="Q151" s="9">
@@ -16258,7 +16293,7 @@
         <v>84</v>
       </c>
       <c r="O152" s="9"/>
-      <c r="P152" s="101">
+      <c r="P152" s="104">
         <v>22009</v>
       </c>
       <c r="Q152" s="9">
@@ -16340,7 +16375,7 @@
         <v>84</v>
       </c>
       <c r="O153" s="9"/>
-      <c r="P153" s="101">
+      <c r="P153" s="104">
         <v>22009</v>
       </c>
       <c r="Q153" s="9">
@@ -16422,7 +16457,7 @@
         <v>84</v>
       </c>
       <c r="O154" s="9"/>
-      <c r="P154" s="101">
+      <c r="P154" s="104">
         <v>22009</v>
       </c>
       <c r="Q154" s="9">
@@ -16580,7 +16615,7 @@
         <v>84</v>
       </c>
       <c r="O156" s="9"/>
-      <c r="P156" s="101">
+      <c r="P156" s="104">
         <v>22009</v>
       </c>
       <c r="Q156" s="9">
@@ -16662,7 +16697,7 @@
         <v>84</v>
       </c>
       <c r="O157" s="9"/>
-      <c r="P157" s="101">
+      <c r="P157" s="104">
         <v>22009</v>
       </c>
       <c r="Q157" s="9">
@@ -16744,7 +16779,7 @@
         <v>84</v>
       </c>
       <c r="O158" s="9"/>
-      <c r="P158" s="101">
+      <c r="P158" s="104">
         <v>22009</v>
       </c>
       <c r="Q158" s="9">
@@ -17069,7 +17104,7 @@
         <v>84</v>
       </c>
       <c r="O162" s="9"/>
-      <c r="P162" s="101">
+      <c r="P162" s="104">
         <v>22009</v>
       </c>
       <c r="Q162" s="9">
@@ -17115,8 +17150,8 @@
       </c>
     </row>
     <row r="163" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A163" s="94"/>
-      <c r="B163" s="95" t="s">
+      <c r="A163" s="97"/>
+      <c r="B163" s="98" t="s">
         <v>331</v>
       </c>
       <c r="C163" s="62"/>
@@ -17200,10 +17235,10 @@
       </c>
     </row>
     <row r="164" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="105" t="s">
+      <c r="A164" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="B164" s="105" t="s">
+      <c r="B164" s="108" t="s">
         <v>71</v>
       </c>
       <c r="C164" s="35"/>
@@ -17255,7 +17290,7 @@
         <v>1</v>
       </c>
       <c r="U164" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V164" s="9"/>
       <c r="W164" s="9">
@@ -17277,13 +17312,10 @@
       </c>
       <c r="AD164" s="30"/>
       <c r="AE164" s="30"/>
-      <c r="AH164" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="165" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A165" s="106"/>
-      <c r="B165" s="106"/>
+      <c r="A165" s="109"/>
+      <c r="B165" s="109"/>
       <c r="C165" s="35"/>
       <c r="D165" s="9">
         <v>4002</v>
@@ -17333,7 +17365,7 @@
         <v>1</v>
       </c>
       <c r="U165" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V165" s="9"/>
       <c r="W165" s="9">
@@ -17355,13 +17387,10 @@
       </c>
       <c r="AD165" s="30"/>
       <c r="AE165" s="30"/>
-      <c r="AH165" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="166" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A166" s="106"/>
-      <c r="B166" s="106"/>
+      <c r="A166" s="109"/>
+      <c r="B166" s="109"/>
       <c r="C166" s="35"/>
       <c r="D166" s="9">
         <v>4003</v>
@@ -17411,7 +17440,7 @@
         <v>1</v>
       </c>
       <c r="U166" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V166" s="9"/>
       <c r="W166" s="9">
@@ -17433,13 +17462,10 @@
       </c>
       <c r="AD166" s="30"/>
       <c r="AE166" s="30"/>
-      <c r="AH166" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="167" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A167" s="106"/>
-      <c r="B167" s="106"/>
+      <c r="A167" s="109"/>
+      <c r="B167" s="109"/>
       <c r="C167" s="35"/>
       <c r="D167" s="9">
         <v>4004</v>
@@ -17489,7 +17515,7 @@
         <v>1</v>
       </c>
       <c r="U167" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V167" s="9"/>
       <c r="W167" s="9">
@@ -17511,13 +17537,10 @@
       </c>
       <c r="AD167" s="30"/>
       <c r="AE167" s="30"/>
-      <c r="AH167" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="168" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A168" s="106"/>
-      <c r="B168" s="106"/>
+      <c r="A168" s="109"/>
+      <c r="B168" s="109"/>
       <c r="C168" s="35"/>
       <c r="D168" s="9">
         <v>4005</v>
@@ -17567,7 +17590,7 @@
         <v>1</v>
       </c>
       <c r="U168" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V168" s="9"/>
       <c r="W168" s="9">
@@ -17589,13 +17612,10 @@
       </c>
       <c r="AD168" s="30"/>
       <c r="AE168" s="30"/>
-      <c r="AH168" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="169" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A169" s="106"/>
-      <c r="B169" s="107"/>
+      <c r="A169" s="109"/>
+      <c r="B169" s="110"/>
       <c r="C169" s="35"/>
       <c r="D169" s="9">
         <v>4006</v>
@@ -17645,7 +17665,7 @@
         <v>1</v>
       </c>
       <c r="U169" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V169" s="9"/>
       <c r="W169" s="9">
@@ -17667,13 +17687,10 @@
       </c>
       <c r="AD169" s="30"/>
       <c r="AE169" s="30"/>
-      <c r="AH169" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="170" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A170" s="106"/>
-      <c r="B170" s="111" t="s">
+      <c r="A170" s="109"/>
+      <c r="B170" s="114" t="s">
         <v>234</v>
       </c>
       <c r="C170" s="35" t="s">
@@ -17727,7 +17744,7 @@
         <v>1</v>
       </c>
       <c r="U170" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V170" s="9"/>
       <c r="W170" s="9">
@@ -17749,13 +17766,10 @@
       </c>
       <c r="AD170" s="30"/>
       <c r="AE170" s="30"/>
-      <c r="AH170" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="171" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A171" s="106"/>
-      <c r="B171" s="111"/>
+      <c r="A171" s="109"/>
+      <c r="B171" s="114"/>
       <c r="C171" s="35" t="s">
         <v>229</v>
       </c>
@@ -17807,7 +17821,7 @@
         <v>1</v>
       </c>
       <c r="U171" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V171" s="9"/>
       <c r="W171" s="9">
@@ -17829,13 +17843,10 @@
       </c>
       <c r="AD171" s="30"/>
       <c r="AE171" s="30"/>
-      <c r="AH171" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="172" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A172" s="106"/>
-      <c r="B172" s="111"/>
+      <c r="A172" s="109"/>
+      <c r="B172" s="114"/>
       <c r="C172" s="35" t="s">
         <v>230</v>
       </c>
@@ -17887,7 +17898,7 @@
         <v>1</v>
       </c>
       <c r="U172" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V172" s="9"/>
       <c r="W172" s="9">
@@ -17909,13 +17920,10 @@
       </c>
       <c r="AD172" s="30"/>
       <c r="AE172" s="30"/>
-      <c r="AH172" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="173" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A173" s="106"/>
-      <c r="B173" s="111"/>
+      <c r="A173" s="109"/>
+      <c r="B173" s="114"/>
       <c r="C173" s="35" t="s">
         <v>231</v>
       </c>
@@ -17967,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="U173" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V173" s="9"/>
       <c r="W173" s="9">
@@ -17989,13 +17997,10 @@
       </c>
       <c r="AD173" s="30"/>
       <c r="AE173" s="30"/>
-      <c r="AH173" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="174" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A174" s="106"/>
-      <c r="B174" s="111"/>
+      <c r="A174" s="109"/>
+      <c r="B174" s="114"/>
       <c r="C174" s="35" t="s">
         <v>232</v>
       </c>
@@ -18047,7 +18052,7 @@
         <v>1</v>
       </c>
       <c r="U174" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V174" s="9"/>
       <c r="W174" s="9">
@@ -18069,13 +18074,10 @@
       </c>
       <c r="AD174" s="30"/>
       <c r="AE174" s="30"/>
-      <c r="AH174" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="175" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A175" s="106"/>
-      <c r="B175" s="111"/>
+      <c r="A175" s="109"/>
+      <c r="B175" s="114"/>
       <c r="C175" s="35" t="s">
         <v>233</v>
       </c>
@@ -18127,7 +18129,7 @@
         <v>1</v>
       </c>
       <c r="U175" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V175" s="9"/>
       <c r="W175" s="9">
@@ -18149,13 +18151,10 @@
       </c>
       <c r="AD175" s="30"/>
       <c r="AE175" s="30"/>
-      <c r="AH175" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="176" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A176" s="106"/>
-      <c r="B176" s="111" t="s">
+      <c r="A176" s="109"/>
+      <c r="B176" s="114" t="s">
         <v>235</v>
       </c>
       <c r="C176" s="35" t="s">
@@ -18209,7 +18208,7 @@
         <v>1</v>
       </c>
       <c r="U176" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V176" s="9"/>
       <c r="W176" s="9">
@@ -18231,13 +18230,10 @@
       </c>
       <c r="AD176" s="30"/>
       <c r="AE176" s="30"/>
-      <c r="AH176" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A177" s="106"/>
-      <c r="B177" s="111"/>
+    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A177" s="109"/>
+      <c r="B177" s="114"/>
       <c r="C177" s="35" t="s">
         <v>237</v>
       </c>
@@ -18289,7 +18285,7 @@
         <v>1</v>
       </c>
       <c r="U177" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V177" s="9"/>
       <c r="W177" s="9">
@@ -18311,13 +18307,10 @@
       </c>
       <c r="AD177" s="30"/>
       <c r="AE177" s="30"/>
-      <c r="AH177" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A178" s="106"/>
-      <c r="B178" s="111"/>
+    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A178" s="109"/>
+      <c r="B178" s="114"/>
       <c r="C178" s="35" t="s">
         <v>238</v>
       </c>
@@ -18369,7 +18362,7 @@
         <v>1</v>
       </c>
       <c r="U178" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V178" s="9"/>
       <c r="W178" s="9">
@@ -18391,13 +18384,10 @@
       </c>
       <c r="AD178" s="30"/>
       <c r="AE178" s="30"/>
-      <c r="AH178" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A179" s="106"/>
-      <c r="B179" s="111"/>
+    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A179" s="109"/>
+      <c r="B179" s="114"/>
       <c r="C179" s="35" t="s">
         <v>239</v>
       </c>
@@ -18449,7 +18439,7 @@
         <v>1</v>
       </c>
       <c r="U179" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V179" s="9"/>
       <c r="W179" s="9">
@@ -18471,13 +18461,10 @@
       </c>
       <c r="AD179" s="30"/>
       <c r="AE179" s="30"/>
-      <c r="AH179" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A180" s="106"/>
-      <c r="B180" s="111"/>
+    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A180" s="109"/>
+      <c r="B180" s="114"/>
       <c r="C180" s="35" t="s">
         <v>240</v>
       </c>
@@ -18529,7 +18516,7 @@
         <v>1</v>
       </c>
       <c r="U180" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V180" s="9"/>
       <c r="W180" s="9">
@@ -18551,13 +18538,10 @@
       </c>
       <c r="AD180" s="30"/>
       <c r="AE180" s="30"/>
-      <c r="AH180" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A181" s="106"/>
-      <c r="B181" s="111"/>
+    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A181" s="109"/>
+      <c r="B181" s="114"/>
       <c r="C181" s="35" t="s">
         <v>241</v>
       </c>
@@ -18609,7 +18593,7 @@
         <v>1</v>
       </c>
       <c r="U181" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V181" s="9"/>
       <c r="W181" s="9">
@@ -18631,13 +18615,10 @@
       </c>
       <c r="AD181" s="30"/>
       <c r="AE181" s="30"/>
-      <c r="AH181" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A182" s="106"/>
-      <c r="B182" s="111"/>
+    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A182" s="109"/>
+      <c r="B182" s="114"/>
       <c r="C182" s="35" t="s">
         <v>242</v>
       </c>
@@ -18689,7 +18670,7 @@
         <v>1</v>
       </c>
       <c r="U182" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V182" s="9"/>
       <c r="W182" s="9">
@@ -18711,13 +18692,10 @@
       </c>
       <c r="AD182" s="30"/>
       <c r="AE182" s="30"/>
-      <c r="AH182" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A183" s="106"/>
-      <c r="B183" s="111" t="s">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A183" s="109"/>
+      <c r="B183" s="114" t="s">
         <v>243</v>
       </c>
       <c r="C183" s="35" t="s">
@@ -18771,7 +18749,7 @@
         <v>1</v>
       </c>
       <c r="U183" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V183" s="9"/>
       <c r="W183" s="9">
@@ -18793,13 +18771,10 @@
       </c>
       <c r="AD183" s="30"/>
       <c r="AE183" s="30"/>
-      <c r="AH183" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A184" s="106"/>
-      <c r="B184" s="111"/>
+    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A184" s="109"/>
+      <c r="B184" s="114"/>
       <c r="C184" s="35" t="s">
         <v>245</v>
       </c>
@@ -18851,7 +18826,7 @@
         <v>1</v>
       </c>
       <c r="U184" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V184" s="9"/>
       <c r="W184" s="9">
@@ -18873,13 +18848,10 @@
       </c>
       <c r="AD184" s="30"/>
       <c r="AE184" s="30"/>
-      <c r="AH184" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A185" s="106"/>
-      <c r="B185" s="111"/>
+    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A185" s="109"/>
+      <c r="B185" s="114"/>
       <c r="C185" s="35" t="s">
         <v>246</v>
       </c>
@@ -18931,7 +18903,7 @@
         <v>1</v>
       </c>
       <c r="U185" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V185" s="9"/>
       <c r="W185" s="9">
@@ -18953,13 +18925,10 @@
       </c>
       <c r="AD185" s="30"/>
       <c r="AE185" s="30"/>
-      <c r="AH185" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A186" s="106"/>
-      <c r="B186" s="111"/>
+    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A186" s="109"/>
+      <c r="B186" s="114"/>
       <c r="C186" s="35" t="s">
         <v>248</v>
       </c>
@@ -19011,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="U186" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V186" s="9"/>
       <c r="W186" s="9">
@@ -19033,13 +19002,10 @@
       </c>
       <c r="AD186" s="30"/>
       <c r="AE186" s="30"/>
-      <c r="AH186" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A187" s="106"/>
-      <c r="B187" s="111"/>
+    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A187" s="109"/>
+      <c r="B187" s="114"/>
       <c r="C187" s="35" t="s">
         <v>247</v>
       </c>
@@ -19091,7 +19057,7 @@
         <v>1</v>
       </c>
       <c r="U187" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V187" s="9"/>
       <c r="W187" s="9">
@@ -19113,13 +19079,10 @@
       </c>
       <c r="AD187" s="30"/>
       <c r="AE187" s="30"/>
-      <c r="AH187" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A188" s="106"/>
-      <c r="B188" s="111" t="s">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A188" s="109"/>
+      <c r="B188" s="114" t="s">
         <v>249</v>
       </c>
       <c r="C188" s="35" t="s">
@@ -19173,7 +19136,7 @@
         <v>1</v>
       </c>
       <c r="U188" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V188" s="9"/>
       <c r="W188" s="9">
@@ -19195,13 +19158,10 @@
       </c>
       <c r="AD188" s="30"/>
       <c r="AE188" s="30"/>
-      <c r="AH188" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A189" s="106"/>
-      <c r="B189" s="111"/>
+    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A189" s="109"/>
+      <c r="B189" s="114"/>
       <c r="C189" s="35" t="s">
         <v>251</v>
       </c>
@@ -19253,7 +19213,7 @@
         <v>1</v>
       </c>
       <c r="U189" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V189" s="9"/>
       <c r="W189" s="9">
@@ -19275,13 +19235,10 @@
       </c>
       <c r="AD189" s="30"/>
       <c r="AE189" s="30"/>
-      <c r="AH189" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A190" s="106"/>
-      <c r="B190" s="111"/>
+    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A190" s="109"/>
+      <c r="B190" s="114"/>
       <c r="C190" s="35" t="s">
         <v>252</v>
       </c>
@@ -19333,7 +19290,7 @@
         <v>1</v>
       </c>
       <c r="U190" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V190" s="9"/>
       <c r="W190" s="9">
@@ -19355,13 +19312,10 @@
       </c>
       <c r="AD190" s="30"/>
       <c r="AE190" s="30"/>
-      <c r="AH190" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A191" s="106"/>
-      <c r="B191" s="111" t="s">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A191" s="109"/>
+      <c r="B191" s="114" t="s">
         <v>253</v>
       </c>
       <c r="C191" s="35" t="s">
@@ -19415,7 +19369,7 @@
         <v>1</v>
       </c>
       <c r="U191" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V191" s="9"/>
       <c r="W191" s="9">
@@ -19437,13 +19391,10 @@
       </c>
       <c r="AD191" s="30"/>
       <c r="AE191" s="30"/>
-      <c r="AH191" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A192" s="106"/>
-      <c r="B192" s="111"/>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A192" s="109"/>
+      <c r="B192" s="114"/>
       <c r="C192" s="35" t="s">
         <v>255</v>
       </c>
@@ -19495,7 +19446,7 @@
         <v>1</v>
       </c>
       <c r="U192" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V192" s="9"/>
       <c r="W192" s="9">
@@ -19517,13 +19468,10 @@
       </c>
       <c r="AD192" s="30"/>
       <c r="AE192" s="30"/>
-      <c r="AH192" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A193" s="106"/>
-      <c r="B193" s="111"/>
+    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A193" s="109"/>
+      <c r="B193" s="114"/>
       <c r="C193" s="35" t="s">
         <v>256</v>
       </c>
@@ -19575,7 +19523,7 @@
         <v>1</v>
       </c>
       <c r="U193" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V193" s="9"/>
       <c r="W193" s="9">
@@ -19597,13 +19545,10 @@
       </c>
       <c r="AD193" s="30"/>
       <c r="AE193" s="30"/>
-      <c r="AH193" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A194" s="106"/>
-      <c r="B194" s="111"/>
+    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A194" s="109"/>
+      <c r="B194" s="114"/>
       <c r="C194" s="35" t="s">
         <v>257</v>
       </c>
@@ -19655,7 +19600,7 @@
         <v>1</v>
       </c>
       <c r="U194" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V194" s="9"/>
       <c r="W194" s="9">
@@ -19677,13 +19622,10 @@
       </c>
       <c r="AD194" s="30"/>
       <c r="AE194" s="30"/>
-      <c r="AH194" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A195" s="106"/>
-      <c r="B195" s="108"/>
+    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A195" s="109"/>
+      <c r="B195" s="111"/>
       <c r="C195" s="35"/>
       <c r="D195" s="9">
         <v>5001</v>
@@ -19733,7 +19675,7 @@
         <v>1</v>
       </c>
       <c r="U195" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V195" s="9"/>
       <c r="W195" s="9">
@@ -19755,13 +19697,10 @@
       </c>
       <c r="AD195" s="30"/>
       <c r="AE195" s="30"/>
-      <c r="AH195" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A196" s="106"/>
-      <c r="B196" s="109"/>
+    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A196" s="109"/>
+      <c r="B196" s="112"/>
       <c r="C196" s="35"/>
       <c r="D196" s="9">
         <v>5002</v>
@@ -19811,7 +19750,7 @@
         <v>1</v>
       </c>
       <c r="U196" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V196" s="9"/>
       <c r="W196" s="9">
@@ -19833,13 +19772,10 @@
       </c>
       <c r="AD196" s="30"/>
       <c r="AE196" s="30"/>
-      <c r="AH196" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A197" s="107"/>
-      <c r="B197" s="110"/>
+    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A197" s="110"/>
+      <c r="B197" s="113"/>
       <c r="C197" s="35"/>
       <c r="D197" s="9">
         <v>5003</v>
@@ -19889,7 +19825,7 @@
         <v>1</v>
       </c>
       <c r="U197" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="V197" s="9"/>
       <c r="W197" s="9">
@@ -19911,11 +19847,8 @@
       </c>
       <c r="AD197" s="30"/>
       <c r="AE197" s="30"/>
-      <c r="AH197" s="2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A198" s="35">
         <v>5</v>
       </c>
@@ -19993,7 +19926,7 @@
       <c r="AE198" s="30"/>
       <c r="AF198" s="14"/>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A199" s="35"/>
       <c r="B199" s="35"/>
       <c r="C199" s="35" t="s">
@@ -20067,7 +20000,7 @@
       <c r="AE199" s="30"/>
       <c r="AF199" s="14"/>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A200" s="35"/>
       <c r="B200" s="35"/>
       <c r="C200" s="35" t="s">
@@ -20141,7 +20074,7 @@
       <c r="AE200" s="30"/>
       <c r="AF200" s="14"/>
     </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A201" s="35"/>
       <c r="B201" s="35"/>
       <c r="C201" s="35" t="s">
@@ -20215,7 +20148,7 @@
       <c r="AE201" s="30"/>
       <c r="AF201" s="14"/>
     </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A202" s="35"/>
       <c r="B202" s="35"/>
       <c r="C202" s="35" t="s">
@@ -20289,7 +20222,7 @@
       <c r="AE202" s="30"/>
       <c r="AF202" s="14"/>
     </row>
-    <row r="203" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A203" s="35"/>
       <c r="B203" s="35"/>
       <c r="C203" s="35" t="s">
@@ -20363,7 +20296,7 @@
       <c r="AE203" s="30"/>
       <c r="AF203" s="14"/>
     </row>
-    <row r="204" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A204" s="35"/>
       <c r="B204" s="35"/>
       <c r="C204" s="35" t="s">
@@ -20437,7 +20370,7 @@
       <c r="AE204" s="30"/>
       <c r="AF204" s="14"/>
     </row>
-    <row r="205" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A205" s="35"/>
       <c r="B205" s="35"/>
       <c r="C205" s="35" t="s">
@@ -20541,25 +20474,25 @@
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="D1:D5 D7 D9:D12 D15:D18 D20:D1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="2110"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="duplicateValues" dxfId="4" priority="2109"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="2109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:D14">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:D14">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5 D7 D9:D12 D15:D18 D20:D163">
-    <cfRule type="duplicateValues" dxfId="1" priority="2172"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="2172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
